--- a/public/crawlability-eraabeauty-september-2026.xlsx
+++ b/public/crawlability-eraabeauty-september-2026.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>כתובות שבורות (404): כתובת אחת (הבולטת: https://eraabeauty.com/collections/essentials, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>כתובות שבורות (404): כתובת אחת; הבולטת https://eraabeauty.com/collections/essentials (קישור נכנס אחד).</t>
         </is>
       </c>
     </row>
